--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0246A7AF-028D-482E-9D70-0A789206F9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A219D7-5D53-4EFC-BF35-CEC6A1038046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1802,16 +1802,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A219D7-5D53-4EFC-BF35-CEC6A1038046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082D809E-2E6A-4BDD-BCDE-ACF5E3DF442B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1037,13 +1037,13 @@
                   <c:v>9.1174338012933731E-3</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>1.108350791037083E-2</c:v>
+                  <c:v>1.0850341059267519E-2</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>1.2519466690719129E-2</c:v>
+                  <c:v>1.1864723637700079E-2</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>1.3725630007684231E-2</c:v>
+                  <c:v>1.258540060371161E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8094,183 +8094,183 @@
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
+      <c r="A100" s="16">
         <v>99</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B100" s="16">
         <v>3.396941596840962</v>
       </c>
-      <c r="C100" s="5">
-        <v>295.73001098632813</v>
-      </c>
-      <c r="D100" s="5">
-        <v>3.3973333835601811</v>
-      </c>
-      <c r="E100" s="5">
-        <v>4.9972328497460694E-7</v>
-      </c>
-      <c r="F100" s="5">
-        <v>1.108350791037083E-2</v>
-      </c>
-      <c r="G100" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" s="5">
-        <v>150</v>
-      </c>
-      <c r="I100" s="5">
-        <v>350</v>
-      </c>
-      <c r="J100" s="5">
-        <v>0.55725306272506714</v>
-      </c>
-      <c r="K100" s="5">
-        <v>0.31053099036216741</v>
-      </c>
-      <c r="L100" s="5">
-        <v>1.3134580649662251E-3</v>
-      </c>
-      <c r="M100" s="5">
-        <v>2.6269161608070139E-3</v>
-      </c>
-      <c r="N100" s="5">
-        <v>3.9178671921868968E-4</v>
-      </c>
-      <c r="O100" s="5">
-        <v>1017.549492123794</v>
-      </c>
-      <c r="P100" s="5">
-        <v>100</v>
-      </c>
-      <c r="Q100" s="6">
-        <v>180000</v>
+      <c r="C100" s="16">
+        <v>296.010009765625</v>
+      </c>
+      <c r="D100" s="16">
+        <v>3.3971948623657231</v>
+      </c>
+      <c r="E100" s="16">
+        <v>6.5445474319858477E-6</v>
+      </c>
+      <c r="F100" s="16">
+        <v>1.0850341059267519E-2</v>
+      </c>
+      <c r="G100" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="16">
+        <v>225</v>
+      </c>
+      <c r="I100" s="16">
+        <v>325</v>
+      </c>
+      <c r="J100" s="16">
+        <v>0.56075197458267212</v>
+      </c>
+      <c r="K100" s="16">
+        <v>0.31444278359413153</v>
+      </c>
+      <c r="L100" s="16">
+        <v>1.40187993645668E-3</v>
+      </c>
+      <c r="M100" s="16">
+        <v>2.8037598822265859E-3</v>
+      </c>
+      <c r="N100" s="16">
+        <v>2.5326552476068192E-4</v>
+      </c>
+      <c r="O100" s="16">
+        <v>2123.5047142568869</v>
+      </c>
+      <c r="P100" s="16">
+        <v>125</v>
+      </c>
+      <c r="Q100" s="16">
+        <v>160000</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100">
         <f t="shared" si="2"/>
-        <v>1.1533513545921359E-2</v>
+        <v>7.4556926441187599E-3</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="4">
+      <c r="A101" s="16">
         <v>100</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B101" s="16">
         <v>3.6598783159560249</v>
       </c>
-      <c r="C101" s="5">
-        <v>277.39999389648438</v>
-      </c>
-      <c r="D101" s="5">
-        <v>3.6595418453216548</v>
-      </c>
-      <c r="E101" s="5">
-        <v>6.4497444327571429E-6</v>
-      </c>
-      <c r="F101" s="5">
-        <v>1.2519466690719129E-2</v>
-      </c>
-      <c r="G101" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H101" s="5">
-        <v>150</v>
-      </c>
-      <c r="I101" s="5">
-        <v>350</v>
-      </c>
-      <c r="J101" s="5">
-        <v>0.5600782036781311</v>
-      </c>
-      <c r="K101" s="5">
-        <v>0.31368759274482733</v>
-      </c>
-      <c r="L101" s="5">
-        <v>9.0856682145031096E-4</v>
-      </c>
-      <c r="M101" s="5">
-        <v>1.8171336269006131E-3</v>
-      </c>
-      <c r="N101" s="5">
-        <v>3.3647063436959002E-4</v>
-      </c>
-      <c r="O101" s="5">
-        <v>1595.028144457008</v>
-      </c>
-      <c r="P101" s="5">
-        <v>100</v>
-      </c>
-      <c r="Q101" s="6">
-        <v>380000</v>
+      <c r="C101" s="16">
+        <v>277.489990234375</v>
+      </c>
+      <c r="D101" s="16">
+        <v>3.659634113311768</v>
+      </c>
+      <c r="E101" s="16">
+        <v>5.9604644775390618E-8</v>
+      </c>
+      <c r="F101" s="16">
+        <v>1.1864723637700079E-2</v>
+      </c>
+      <c r="G101" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="16">
+        <v>225</v>
+      </c>
+      <c r="I101" s="16">
+        <v>325</v>
+      </c>
+      <c r="J101" s="16">
+        <v>0.55893903970718384</v>
+      </c>
+      <c r="K101" s="16">
+        <v>0.31241282820701599</v>
+      </c>
+      <c r="L101" s="16">
+        <v>1.056295497936046E-3</v>
+      </c>
+      <c r="M101" s="16">
+        <v>2.112590940669179E-3</v>
+      </c>
+      <c r="N101" s="16">
+        <v>2.4420264425728527E-4</v>
+      </c>
+      <c r="O101" s="16">
+        <v>887.96277450411105</v>
+      </c>
+      <c r="P101" s="16">
+        <v>125</v>
+      </c>
+      <c r="Q101" s="16">
+        <v>280000</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>
       </c>
       <c r="S101">
         <f t="shared" si="2"/>
-        <v>9.1934923875111926E-3</v>
+        <v>6.6724252331732299E-3</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
+      <c r="A102" s="16">
         <v>101</v>
       </c>
-      <c r="B102" s="5">
+      <c r="B102" s="16">
         <v>3.9287583783681899</v>
       </c>
-      <c r="C102" s="5">
-        <v>261.91000366210938</v>
-      </c>
-      <c r="D102" s="5">
-        <v>3.9291176795959468</v>
-      </c>
-      <c r="E102" s="5">
-        <v>2.3479929041059222E-6</v>
-      </c>
-      <c r="F102" s="5">
-        <v>1.3725630007684231E-2</v>
-      </c>
-      <c r="G102" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H102" s="5">
-        <v>150</v>
-      </c>
-      <c r="I102" s="5">
-        <v>350</v>
-      </c>
-      <c r="J102" s="5">
-        <v>0.56195908784866333</v>
-      </c>
-      <c r="K102" s="5">
-        <v>0.31579798460006708</v>
-      </c>
-      <c r="L102" s="5">
-        <v>1.6222361532149121E-3</v>
-      </c>
-      <c r="M102" s="5">
-        <v>3.2444724347442389E-3</v>
-      </c>
-      <c r="N102" s="5">
-        <v>3.5930122775740259E-4</v>
-      </c>
-      <c r="O102" s="5">
-        <v>82.93836134603221</v>
-      </c>
-      <c r="P102" s="5">
-        <v>100</v>
-      </c>
-      <c r="Q102" s="6">
-        <v>120000</v>
+      <c r="C102" s="16">
+        <v>261.69000244140619</v>
+      </c>
+      <c r="D102" s="16">
+        <v>3.9284789562225342</v>
+      </c>
+      <c r="E102" s="16">
+        <v>1.20686563604977E-5</v>
+      </c>
+      <c r="F102" s="16">
+        <v>1.258540060371161E-2</v>
+      </c>
+      <c r="G102" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H102" s="16">
+        <v>225</v>
+      </c>
+      <c r="I102" s="16">
+        <v>325</v>
+      </c>
+      <c r="J102" s="16">
+        <v>0.56471312046051025</v>
+      </c>
+      <c r="K102" s="16">
+        <v>0.31890091300010681</v>
+      </c>
+      <c r="L102" s="16">
+        <v>3.9931247690264248E-3</v>
+      </c>
+      <c r="M102" s="16">
+        <v>7.9862494021654129E-3</v>
+      </c>
+      <c r="N102" s="16">
+        <v>2.7942214565568341E-4</v>
+      </c>
+      <c r="O102" s="16">
+        <v>24.661866731702229</v>
+      </c>
+      <c r="P102" s="16">
+        <v>125</v>
+      </c>
+      <c r="Q102" s="16">
+        <v>20000</v>
       </c>
       <c r="R102" t="b">
         <v>0</v>
       </c>
       <c r="S102">
         <f t="shared" si="2"/>
-        <v>9.1454142289767986E-3</v>
+        <v>7.1122252565641725E-3</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>5.7030419965651898E-2</v>
+        <v>5.6944953856458307E-2</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="S105">
         <f>_xlfn.STDEV.S(S2:S102)</f>
-        <v>0.10810331284749324</v>
+        <v>0.10814185039046972</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082D809E-2E6A-4BDD-BCDE-ACF5E3DF442B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F0D5FF-A363-469D-9A29-461B8269C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1034,7 +1034,7 @@
                   <c:v>8.1189507618546486E-3</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>9.1174338012933731E-3</c:v>
+                  <c:v>9.36083123087883E-3</c:v>
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>1.0850341059267519E-2</c:v>
@@ -8034,63 +8034,63 @@
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99" s="4">
+      <c r="A99" s="16">
         <v>98</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B99" s="16">
         <v>3.1426150900261072</v>
       </c>
-      <c r="C99" s="5">
-        <v>317.3800048828125</v>
-      </c>
-      <c r="D99" s="5">
-        <v>3.1429083347320561</v>
-      </c>
-      <c r="E99" s="5">
-        <v>4.9800291890278459E-8</v>
-      </c>
-      <c r="F99" s="5">
-        <v>9.1174338012933731E-3</v>
-      </c>
-      <c r="G99" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" s="5">
-        <v>250</v>
-      </c>
-      <c r="I99" s="5">
-        <v>450</v>
-      </c>
-      <c r="J99" s="5">
-        <v>0.55955517292022705</v>
-      </c>
-      <c r="K99" s="5">
-        <v>0.31310197710990911</v>
-      </c>
-      <c r="L99" s="5">
-        <v>1.6152966485597029E-3</v>
-      </c>
-      <c r="M99" s="5">
-        <v>3.2305934000760321E-3</v>
-      </c>
-      <c r="N99" s="5">
-        <v>2.9324470594849222E-4</v>
-      </c>
-      <c r="O99" s="5">
-        <v>375.92809524698453</v>
-      </c>
-      <c r="P99" s="5">
-        <v>100</v>
-      </c>
-      <c r="Q99" s="6">
-        <v>120000</v>
+      <c r="C99" s="16">
+        <v>317.44000244140619</v>
+      </c>
+      <c r="D99" s="16">
+        <v>3.142382144927979</v>
+      </c>
+      <c r="E99" s="16">
+        <v>1.2216537470521871E-7</v>
+      </c>
+      <c r="F99" s="16">
+        <v>9.36083123087883E-3</v>
+      </c>
+      <c r="G99" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="16">
+        <v>275</v>
+      </c>
+      <c r="I99" s="16">
+        <v>375</v>
+      </c>
+      <c r="J99" s="16">
+        <v>0.55945098400115967</v>
+      </c>
+      <c r="K99" s="16">
+        <v>0.31298542022705078</v>
+      </c>
+      <c r="L99" s="16">
+        <v>1.0971736478156151E-3</v>
+      </c>
+      <c r="M99" s="16">
+        <v>2.194347325712442E-3</v>
+      </c>
+      <c r="N99" s="16">
+        <v>2.329450981286563E-4</v>
+      </c>
+      <c r="O99" s="16">
+        <v>2853.0617940883499</v>
+      </c>
+      <c r="P99" s="16">
+        <v>150</v>
+      </c>
+      <c r="Q99" s="16">
+        <v>260000</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
       </c>
       <c r="S99">
         <f t="shared" si="2"/>
-        <v>9.3312320328117586E-3</v>
+        <v>7.4124603699628096E-3</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="S103">
         <f>AVERAGE(S2:S102)</f>
-        <v>5.6944953856458307E-2</v>
+        <v>5.6925956117222176E-2</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="S105">
         <f>_xlfn.STDEV.S(S2:S102)</f>
-        <v>0.10814185039046972</v>
+        <v>0.10815046673686805</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_convergence_fix_mk_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F0D5FF-A363-469D-9A29-461B8269C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DE1A43-D9EC-4833-85E9-A9E4D1E3D6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -989,7 +989,7 @@
                   <c:v>1.1722173076122999E-3</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>1.40053400807828E-3</c:v>
+                  <c:v>1.211138325743377E-3</c:v>
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>1.278836745768785E-3</c:v>
@@ -1803,15 +1803,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>790575</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7148,8 +7148,8 @@
         <f t="shared" si="3"/>
         <v>2.722444478873448E-11</v>
       </c>
-      <c r="F84">
-        <v>1.40053400807828E-3</v>
+      <c r="F84" s="16">
+        <v>1.211138325743377E-3</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
